--- a/data/trans_orig/KP10in_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por tutor (escala)</t>
+          <t>KIDSCREEN percibido por tutor (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,28; 71,53</t>
+          <t>65,28; 71,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,73; 69,93</t>
+          <t>58,72; 69,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,87; 69,58</t>
+          <t>61,8; 69,62</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,55; 70,05</t>
+          <t>63,76; 69,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,83; 69,82</t>
+          <t>62,78; 69,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,07; 68,79</t>
+          <t>64,13; 68,69</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,55; 73,38</t>
+          <t>64,04; 73,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,82; 70,88</t>
+          <t>63,68; 71,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,04; 70,83</t>
+          <t>65,01; 70,75</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,9; 66,91</t>
+          <t>57,12; 66,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,7; 66,6</t>
+          <t>60,8; 67,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,4; 65,52</t>
+          <t>59,83; 65,57</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>63,95; 69,6</t>
+          <t>63,77; 69,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61,27; 65,88</t>
+          <t>61,17; 66,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,17; 66,59</t>
+          <t>63,13; 66,78</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59,59; 66,38</t>
+          <t>59,31; 66,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,38; 68,23</t>
+          <t>60,35; 68,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60,98; 66,35</t>
+          <t>61,02; 66,2</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,8; 67,14</t>
+          <t>62,58; 67,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,94; 66,29</t>
+          <t>62,89; 66,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,55; 66,14</t>
+          <t>63,43; 66,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por tutor (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,28; 71,65</t>
+          <t>65,12; 71,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,72; 69,57</t>
+          <t>57,89; 69,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,8; 69,62</t>
+          <t>62,07; 69,59</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,76; 69,94</t>
+          <t>63,48; 69,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,78; 69,5</t>
+          <t>62,66; 69,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,13; 68,69</t>
+          <t>64,05; 68,86</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,04; 73,38</t>
+          <t>64,33; 74,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,68; 71,2</t>
+          <t>63,62; 71,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,01; 70,75</t>
+          <t>64,76; 70,78</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,12; 66,82</t>
+          <t>57,42; 67,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,8; 67,01</t>
+          <t>61,02; 66,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,83; 65,57</t>
+          <t>59,96; 65,58</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>63,77; 69,5</t>
+          <t>64,15; 69,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61,17; 66,0</t>
+          <t>61,46; 65,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,13; 66,78</t>
+          <t>63,0; 66,74</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59,31; 66,06</t>
+          <t>59,6; 66,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,35; 68,46</t>
+          <t>60,62; 68,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,02; 66,2</t>
+          <t>60,79; 66,33</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,58; 67,06</t>
+          <t>62,94; 67,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,89; 66,04</t>
+          <t>62,9; 66,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,43; 66,14</t>
+          <t>63,42; 66,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Clase-trans_orig.xlsx
@@ -489,18 +489,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por adulto (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>68,22</t>
+          <t>68,51</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>65,76</t>
+          <t>68,53</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66,78</t>
+          <t>68,52</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,12; 71,64</t>
+          <t>65,11; 71,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,89; 69,77</t>
+          <t>65,75; 71,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,07; 69,59</t>
+          <t>66,24; 70,87</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66,74</t>
+          <t>65,99</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66,08</t>
+          <t>66,88</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66,41</t>
+          <t>66,45</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,48; 69,97</t>
+          <t>62,68; 69,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,66; 69,97</t>
+          <t>63,76; 70,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,05; 68,86</t>
+          <t>64,01; 68,83</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>68,63</t>
+          <t>67,19</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>67,26</t>
+          <t>69,13</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67,9</t>
+          <t>68,14</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,33; 74,05</t>
+          <t>63,82; 70,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,62; 71,17</t>
+          <t>64,91; 73,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,76; 70,78</t>
+          <t>65,33; 71,44</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>63,07</t>
+          <t>63,56</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63,47</t>
+          <t>65,54</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63,27</t>
+          <t>64,45</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,42; 67,08</t>
+          <t>60,85; 66,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,02; 66,86</t>
+          <t>63,05; 67,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,96; 65,58</t>
+          <t>62,54; 66,46</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>66,68</t>
+          <t>63,23</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63,7</t>
+          <t>66,95</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64,91</t>
+          <t>64,81</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>64,15; 69,63</t>
+          <t>60,77; 65,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61,46; 65,92</t>
+          <t>64,34; 69,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,0; 66,74</t>
+          <t>63,03; 66,59</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>62,62</t>
+          <t>63,79</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64,18</t>
+          <t>62,26</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63,46</t>
+          <t>63,06</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59,6; 66,19</t>
+          <t>60,01; 68,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,62; 68,74</t>
+          <t>59,01; 66,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60,79; 66,33</t>
+          <t>60,62; 65,87</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>65,5</t>
+          <t>65,04</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>64,68</t>
+          <t>66,46</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65,05</t>
+          <t>65,69</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,94; 67,14</t>
+          <t>63,77; 66,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,9; 66,09</t>
+          <t>65,3; 67,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,42; 66,16</t>
+          <t>64,7; 66,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Clase-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 49,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>68,51</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>68,53</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>68,52</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>68.5132771860075</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>68.52502033514848</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>68.51845424015457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>65,11; 71,82</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>65,75; 71,86</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>66,24; 70,87</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>65.10898659282797</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>65.74559259182809</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>66.23965023693148</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>71.82323229003735</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>71.85833731233325</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>70.87227084544762</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>65,99</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>66,88</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>66,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>62,68; 69,61</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>63,76; 70,25</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>64,01; 68,83</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>65.99429283421614</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>66.88112536899126</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>66.44790631072098</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>67,19</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>69,13</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>68,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>62.68448520606085</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>63.75777060609661</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>64.00649877083606</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>63,82; 70,9</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>64,91; 73,99</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>65,33; 71,44</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>69.61351998154227</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>70.24713009824895</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>68.82564956315829</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,149 +661,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>63,56</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>65,54</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>64,45</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>67.18692292678867</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>69.13363948655575</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>68.14229680806396</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>60,85; 66,64</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>63,05; 67,9</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62,54; 66,46</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>63.81520248490131</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>64.91377403072995</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>65.32577820169087</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>70.90368573038245</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>73.99284391056527</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>71.43517928303778</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>63,23</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>66,95</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>64,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>60,77; 65,47</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>64,34; 69,88</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>63,03; 66,59</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>63.55676231505243</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>65.5380780554041</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>64.44671386594813</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>63,79</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>62,26</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>63,06</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>60.84796954461502</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>63.0542606502711</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>62.54104713791723</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>60,01; 68,04</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>59,01; 66,01</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>60,62; 65,87</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>66.64073611625894</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>67.89929301123185</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>66.46129550866431</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -846,47 +771,162 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>65,04</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>66,46</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>65,69</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>63.22721596409558</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>66.95312793861697</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>64.80513643648213</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>63,77; 66,5</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>65,3; 67,71</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>64,7; 66,57</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>60.77044736005429</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>64.33800733641877</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>63.0264298031412</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>65.47287663161123</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>69.8784085432581</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>66.58666292543455</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>63.79363866919635</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>62.26420075919877</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>63.0568990951809</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>60.01220304543177</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>59.01097046780263</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>60.61733430400847</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>68.0381579830881</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>66.01307336880473</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>65.8720532033684</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>65.0384649312825</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>66.45870758906709</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>65.69059429613912</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>63.76546569468794</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>65.29839790880241</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>64.69841696938664</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>66.49737226956174</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>67.70740017998392</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>66.57213704458175</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -894,14 +934,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
